--- a/cronbach_alpha_results.xlsx
+++ b/cronbach_alpha_results.xlsx
@@ -471,7 +471,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8028</v>
+        <v>0.8274</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8603</v>
+        <v>0.8756</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8313</v>
+        <v>0.8396</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7781</v>
+        <v>0.7816</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8064</v>
+        <v>0.8335</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8083</v>
+        <v>0.829</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8199</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -695,19 +695,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.606</v>
+        <v>3.593</v>
       </c>
       <c r="E2" t="n">
-        <v>1.177</v>
+        <v>1.183</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6262</v>
+        <v>0.6631</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7521</v>
+        <v>0.7813</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8028</v>
+        <v>0.8274</v>
       </c>
       <c r="I2" t="inlineStr"/>
     </row>
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.731</v>
+        <v>3.746</v>
       </c>
       <c r="E3" t="n">
-        <v>1.104</v>
+        <v>1.101</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5424</v>
+        <v>0.5957</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7781</v>
+        <v>0.8008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8028</v>
+        <v>0.8274</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.482</v>
+        <v>3.466</v>
       </c>
       <c r="E4" t="n">
-        <v>1.151</v>
+        <v>1.131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6011</v>
+        <v>0.6233</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7603</v>
+        <v>0.7931</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8028</v>
+        <v>0.8274</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.373</v>
+        <v>3.36</v>
       </c>
       <c r="E5" t="n">
-        <v>1.157</v>
+        <v>1.164</v>
       </c>
       <c r="F5" t="n">
-        <v>0.583</v>
+        <v>0.6109</v>
       </c>
       <c r="G5" t="n">
-        <v>0.766</v>
+        <v>0.7967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8028</v>
+        <v>0.8274</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -827,19 +827,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.715</v>
+        <v>3.733</v>
       </c>
       <c r="E6" t="n">
-        <v>1.176</v>
+        <v>1.156</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5778</v>
+        <v>0.6233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7677</v>
+        <v>0.7931</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8028</v>
+        <v>0.8274</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.674</v>
+        <v>3.682</v>
       </c>
       <c r="E7" t="n">
-        <v>1.209</v>
+        <v>1.191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.706</v>
+        <v>0.7318</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8239</v>
+        <v>0.8425</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8603</v>
+        <v>0.8756</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.518</v>
+        <v>3.559</v>
       </c>
       <c r="E8" t="n">
-        <v>1.225</v>
+        <v>1.207</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6924</v>
+        <v>0.727</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8275</v>
+        <v>0.8437</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8603</v>
+        <v>0.8756</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.451</v>
+        <v>3.466</v>
       </c>
       <c r="E9" t="n">
-        <v>1.233</v>
+        <v>1.218</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6614</v>
+        <v>0.6817</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8356</v>
+        <v>0.855</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8603</v>
+        <v>0.8756</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.855</v>
+        <v>3.881</v>
       </c>
       <c r="E10" t="n">
-        <v>1.141</v>
+        <v>1.108</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6909</v>
+        <v>0.7071</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8283</v>
+        <v>0.849</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8603</v>
+        <v>0.8756</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.736</v>
+        <v>3.775</v>
       </c>
       <c r="E11" t="n">
-        <v>1.185</v>
+        <v>1.158</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6392</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8409</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8603</v>
+        <v>0.8756</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.497</v>
+        <v>3.517</v>
       </c>
       <c r="E12" t="n">
-        <v>1.036</v>
+        <v>1.017</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6368</v>
+        <v>0.6562</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7956</v>
+        <v>0.8037</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8313</v>
+        <v>0.8396</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.549</v>
+        <v>3.538</v>
       </c>
       <c r="E13" t="n">
-        <v>1.055</v>
+        <v>1.045</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6584</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7955</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8313</v>
+        <v>0.8396</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.337</v>
+        <v>3.322</v>
       </c>
       <c r="E14" t="n">
-        <v>1.111</v>
+        <v>1.106</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5745</v>
+        <v>0.5662</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8139</v>
+        <v>0.8295</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8313</v>
+        <v>0.8396</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.368</v>
+        <v>3.356</v>
       </c>
       <c r="E15" t="n">
-        <v>1.068</v>
+        <v>1.052</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6513</v>
+        <v>0.6728</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7912</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8313</v>
+        <v>0.8396</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.627</v>
+        <v>3.636</v>
       </c>
       <c r="E16" t="n">
-        <v>1.029</v>
+        <v>1.016</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6514</v>
+        <v>0.667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7916</v>
+        <v>0.8008</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8313</v>
+        <v>0.8396</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -1190,19 +1190,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.653</v>
+        <v>3.665</v>
       </c>
       <c r="E17" t="n">
-        <v>1.237</v>
+        <v>1.218</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5826</v>
+        <v>0.5844</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7268</v>
+        <v>0.7318</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7781</v>
+        <v>0.7816</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.212</v>
+        <v>3.208</v>
       </c>
       <c r="E18" t="n">
         <v>1.066</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6081</v>
+        <v>0.6151</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7198</v>
+        <v>0.7227</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7781</v>
+        <v>0.7816</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.549</v>
+        <v>3.568</v>
       </c>
       <c r="E19" t="n">
-        <v>1.065</v>
+        <v>1.039</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5081</v>
+        <v>0.5228</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7512</v>
+        <v>0.752</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7781</v>
+        <v>0.7816</v>
       </c>
       <c r="I19" t="inlineStr"/>
     </row>
@@ -1289,19 +1289,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.948</v>
+        <v>2.949</v>
       </c>
       <c r="E20" t="n">
-        <v>1.176</v>
+        <v>1.162</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4736</v>
+        <v>0.4589</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7638</v>
+        <v>0.7739</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7781</v>
+        <v>0.7816</v>
       </c>
       <c r="I20" t="inlineStr"/>
     </row>
@@ -1325,16 +1325,16 @@
         <v>3.487</v>
       </c>
       <c r="E21" t="n">
-        <v>1.146</v>
+        <v>1.135</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5959</v>
+        <v>0.6123</v>
       </c>
       <c r="G21" t="n">
         <v>0.722</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7781</v>
+        <v>0.7816</v>
       </c>
       <c r="I21" t="inlineStr"/>
     </row>
@@ -1355,19 +1355,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3.933</v>
+        <v>3.932</v>
       </c>
       <c r="E22" t="n">
-        <v>1.114</v>
+        <v>1.101</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6157</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7617</v>
+        <v>0.7926</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8064</v>
+        <v>0.8335</v>
       </c>
       <c r="I22" t="inlineStr"/>
     </row>
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3.964</v>
+        <v>3.979</v>
       </c>
       <c r="E23" t="n">
-        <v>1.038</v>
+        <v>1.037</v>
       </c>
       <c r="F23" t="n">
-        <v>0.671</v>
+        <v>0.7222</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7472</v>
+        <v>0.777</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8064</v>
+        <v>0.8335</v>
       </c>
       <c r="I23" t="inlineStr"/>
     </row>
@@ -1421,19 +1421,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.995</v>
+        <v>4.025</v>
       </c>
       <c r="E24" t="n">
-        <v>1.281</v>
+        <v>1.248</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4996</v>
+        <v>0.5154</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8031</v>
+        <v>0.8381</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8064</v>
+        <v>0.8335</v>
       </c>
       <c r="I24" t="inlineStr"/>
     </row>
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.876</v>
+        <v>3.894</v>
       </c>
       <c r="E25" t="n">
-        <v>1.218</v>
+        <v>1.2</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6143</v>
+        <v>0.6621</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7623</v>
+        <v>0.7921</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8064</v>
+        <v>0.8335</v>
       </c>
       <c r="I25" t="inlineStr"/>
     </row>
@@ -1487,19 +1487,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4.047</v>
+        <v>4.059</v>
       </c>
       <c r="E26" t="n">
-        <v>0.964</v>
+        <v>0.961</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5939</v>
+        <v>0.6434</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7712</v>
+        <v>0.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8064</v>
+        <v>0.8335</v>
       </c>
       <c r="I26" t="inlineStr"/>
     </row>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.58</v>
+        <v>3.564</v>
       </c>
       <c r="E27" t="n">
-        <v>1.148</v>
+        <v>1.141</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6211</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7635</v>
+        <v>0.7897</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8083</v>
+        <v>0.829</v>
       </c>
       <c r="I27" t="inlineStr"/>
     </row>
@@ -1553,19 +1553,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3.829</v>
+        <v>3.814</v>
       </c>
       <c r="E28" t="n">
-        <v>1.024</v>
+        <v>1.027</v>
       </c>
       <c r="F28" t="n">
-        <v>0.593</v>
+        <v>0.6402</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.791</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8083</v>
+        <v>0.829</v>
       </c>
       <c r="I28" t="inlineStr"/>
     </row>
@@ -1586,19 +1586,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.912</v>
+        <v>3.919</v>
       </c>
       <c r="E29" t="n">
-        <v>1.045</v>
+        <v>1.022</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6112</v>
+        <v>0.6458</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7661</v>
+        <v>0.7894</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8083</v>
+        <v>0.829</v>
       </c>
       <c r="I29" t="inlineStr"/>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3.57</v>
+        <v>3.568</v>
       </c>
       <c r="E30" t="n">
-        <v>1.029</v>
+        <v>1.035</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5889</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7729</v>
+        <v>0.8008</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8083</v>
+        <v>0.829</v>
       </c>
       <c r="I30" t="inlineStr"/>
     </row>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.751</v>
+        <v>3.754</v>
       </c>
       <c r="E31" t="n">
-        <v>0.99</v>
+        <v>0.984</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5605</v>
+        <v>0.5954</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7814</v>
+        <v>0.8035</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8083</v>
+        <v>0.829</v>
       </c>
       <c r="I31" t="inlineStr"/>
     </row>
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.777</v>
+        <v>3.792</v>
       </c>
       <c r="E32" t="n">
-        <v>1.093</v>
+        <v>1.085</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6291</v>
+        <v>0.6538</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7794</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8199</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="I32" t="inlineStr"/>
     </row>
@@ -1718,19 +1718,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.021</v>
+        <v>4.042</v>
       </c>
       <c r="E33" t="n">
-        <v>1.02</v>
+        <v>1.001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5802</v>
+        <v>0.6202</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7935</v>
+        <v>0.8158</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8199</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="I33" t="inlineStr"/>
     </row>
@@ -1751,19 +1751,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.855</v>
+        <v>3.886</v>
       </c>
       <c r="E34" t="n">
-        <v>0.984</v>
+        <v>0.972</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.7088</v>
       </c>
       <c r="G34" t="n">
-        <v>0.77</v>
+        <v>0.793</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8199</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="I34" t="inlineStr"/>
     </row>
@@ -1784,19 +1784,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.896</v>
+        <v>3.919</v>
       </c>
       <c r="E35" t="n">
-        <v>1.031</v>
+        <v>1.001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6266</v>
+        <v>0.6512</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7802</v>
+        <v>0.8076</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8199</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="I35" t="inlineStr"/>
     </row>
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.756</v>
+        <v>3.78</v>
       </c>
       <c r="E36" t="n">
-        <v>1.117</v>
+        <v>1.096</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5654</v>
+        <v>0.6025</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7994</v>
+        <v>0.8219</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8199</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="I36" t="inlineStr"/>
     </row>
